--- a/vch1101/files/kahoot/VCH1101_Kahoot_Unit2.xlsx
+++ b/vch1101/files/kahoot/VCH1101_Kahoot_Unit2.xlsx
@@ -712,17 +712,17 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
+          <t>主管／客戶</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
           <t>朋友</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>同事</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>主管／客戶</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="H9" s="23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" s="1" t="n"/>
@@ -822,12 +822,12 @@
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
+          <t>彼此／互相</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
+        <is>
           <t>要</t>
-        </is>
-      </c>
-      <c r="E12" s="25" t="inlineStr">
-        <is>
-          <t>彼此／互相</t>
         </is>
       </c>
       <c r="F12" s="25" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="H12" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" s="1" t="n"/>
@@ -856,17 +856,17 @@
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
+          <t>估答案</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>由最短嘅詞開始排</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
           <t>搵主語同主要動作</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>由最短嘅詞開始排</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
-        <is>
-          <t>估答案</t>
         </is>
       </c>
       <c r="F13" s="25" t="inlineStr"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="H13" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -891,22 +891,22 @@
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
+          <t>宿舍的同事，</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>請於本週五前交回表格。</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
           <t>申請</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>輪侯</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="inlineStr">
-        <is>
-          <t>宿舍的同事，</t>
-        </is>
-      </c>
-      <c r="F14" s="25" t="inlineStr">
-        <is>
-          <t>請於本週五前交回表格。</t>
         </is>
       </c>
       <c r="G14" s="25" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="H14" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I14" s="1" t="n"/>
@@ -930,12 +930,12 @@
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
+          <t>志</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
           <t>標</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>志</t>
         </is>
       </c>
       <c r="E15" s="25" t="inlineStr"/>
@@ -945,7 +945,7 @@
       </c>
       <c r="H15" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I15" s="1" t="n"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
+          <t>同事</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
           <t>朋友</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>同事</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H16" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I16" s="1" t="n"/>
@@ -996,22 +996,22 @@
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
+          <t>工具。</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>清點</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
           <t>小明</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>正在</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="inlineStr">
-        <is>
-          <t>清點</t>
-        </is>
-      </c>
-      <c r="F17" s="25" t="inlineStr">
-        <is>
-          <t>工具。</t>
         </is>
       </c>
       <c r="G17" s="25" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H17" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" s="1" t="n"/>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
+          <t>搭配錯（拍錯擋）</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
           <t>語序亂（次序錯）</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>搭配錯（拍錯擋）</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H18" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" s="1" t="n"/>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
+          <t>截止日期／最後一天。</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
           <t>6月30日</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="E19" s="25" t="inlineStr">
         <is>
           <t>是</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="inlineStr">
-        <is>
-          <t>截止日期／最後一天。</t>
         </is>
       </c>
       <c r="F19" s="25" t="inlineStr"/>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H19" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" s="1" t="n"/>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
+          <t>一想就</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
+        <is>
           <t>今天事情</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>一想就</t>
         </is>
       </c>
       <c r="F20" s="25" t="inlineStr"/>
@@ -1140,17 +1140,17 @@
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
+          <t>尊</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>請</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
           <t>早市期間，</t>
-        </is>
-      </c>
-      <c r="D21" s="25" t="inlineStr">
-        <is>
-          <t>請</t>
-        </is>
-      </c>
-      <c r="E21" s="25" t="inlineStr">
-        <is>
-          <t>尊</t>
         </is>
       </c>
       <c r="F21" s="25" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H21" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" s="1" t="n"/>
@@ -1210,17 +1210,17 @@
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
+          <t>主管／客戶</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
           <t>朋友</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>同事</t>
-        </is>
-      </c>
-      <c r="E23" s="25" t="inlineStr">
-        <is>
-          <t>主管／客戶</t>
         </is>
       </c>
       <c r="F23" s="25" t="inlineStr"/>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="H23" s="26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I23" s="1" t="n"/>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
+          <t>清點</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
+        <is>
+          <t>工具。</t>
+        </is>
+      </c>
+      <c r="F24" s="25" t="inlineStr">
+        <is>
           <t>正在</t>
-        </is>
-      </c>
-      <c r="E24" s="25" t="inlineStr">
-        <is>
-          <t>清點</t>
-        </is>
-      </c>
-      <c r="F24" s="25" t="inlineStr">
-        <is>
-          <t>工具。</t>
         </is>
       </c>
       <c r="G24" s="25" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H24" s="26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I24" s="1" t="n"/>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
+          <t>搭配錯（拍錯擋）</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr">
+        <is>
           <t>語序亂（次序錯）</t>
-        </is>
-      </c>
-      <c r="D25" s="25" t="inlineStr">
-        <is>
-          <t>搭配錯（拍錯擋）</t>
         </is>
       </c>
       <c r="E25" s="25" t="inlineStr">
@@ -1319,17 +1319,17 @@
       </c>
       <c r="C26" s="25" t="inlineStr">
         <is>
+          <t>突然／漸漸地</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>停了下來。</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
+        <is>
           <t>他</t>
-        </is>
-      </c>
-      <c r="D26" s="25" t="inlineStr">
-        <is>
-          <t>突然／漸漸地</t>
-        </is>
-      </c>
-      <c r="E26" s="25" t="inlineStr">
-        <is>
-          <t>停了下來。</t>
         </is>
       </c>
       <c r="F26" s="25" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H26" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I26" s="1" t="n"/>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="D27" s="25" t="inlineStr">
         <is>
+          <t>只能放主語前</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
           <t>只能放句尾</t>
-        </is>
-      </c>
-      <c r="E27" s="25" t="inlineStr">
-        <is>
-          <t>只能放主語前</t>
         </is>
       </c>
       <c r="F27" s="25" t="inlineStr"/>
@@ -1389,22 +1389,22 @@
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
+          <t>請</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>聯洛。</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
+        <is>
           <t>貨倉補貨，</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
-        <is>
-          <t>請</t>
-        </is>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
+      <c r="F28" s="25" t="inlineStr">
         <is>
           <t>速</t>
-        </is>
-      </c>
-      <c r="F28" s="25" t="inlineStr">
-        <is>
-          <t>聯洛。</t>
         </is>
       </c>
       <c r="G28" s="25" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H28" s="26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" s="1" t="n"/>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
+          <t>緝</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
           <t>編</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>緝</t>
         </is>
       </c>
       <c r="E29" s="27" t="inlineStr"/>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H29" s="28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I29" s="1" t="n"/>
